--- a/jeaf-generator/src/main/resources/Breaking_Change_Report_Template.xlsx
+++ b/jeaf-generator/src/main/resources/Breaking_Change_Report_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A25722-840F-934A-ACD6-3B8034AE6408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F7BBC5-68D7-064A-BEE6-325E2F2001A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4640" yWindow="620" windowWidth="29960" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -59,7 +59,7 @@
     <t>Active with</t>
   </si>
   <si>
-    <t>Activation Date</t>
+    <t>Go Live  Date</t>
   </si>
 </sst>
 </file>
@@ -142,25 +142,25 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -178,12 +178,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -210,11 +204,17 @@
       </border>
     </dxf>
     <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color theme="4"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -230,16 +230,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:G1048576" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4" headerRowBorderDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:G1048576" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
   <autoFilter ref="A1:G1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="4"/>
     <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="3"/>
     <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="2"/>
     <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Activation Date" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live  Date" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/jeaf-generator/src/main/resources/Breaking_Change_Report_Template.xlsx
+++ b/jeaf-generator/src/main/resources/Breaking_Change_Report_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F7BBC5-68D7-064A-BEE6-325E2F2001A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C823A2-D35B-9242-AF25-689A1C616038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4640" yWindow="620" windowWidth="29960" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Package</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Go Live  Date</t>
+  </si>
+  <si>
+    <t>End of Compatibility Phase</t>
   </si>
 </sst>
 </file>
@@ -128,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -162,12 +165,18 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -230,16 +239,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:G1048576" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
-  <autoFilter ref="A1:G1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live  Date" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:H1048576" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
+  <autoFilter ref="A1:H1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live  Date" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{BA3D9D58-4D63-3545-A4C7-20399432C0A1}" name="End of Compatibility Phase" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -562,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1136C3-A1B3-DD42-A00A-DCFCD8D149EA}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.5" style="9" customWidth="1"/>
@@ -571,9 +581,10 @@
     <col min="4" max="4" width="60.33203125" style="9" customWidth="1"/>
     <col min="5" max="5" width="31.5" style="10" customWidth="1"/>
     <col min="6" max="7" width="31.5" style="11" customWidth="1"/>
+    <col min="8" max="8" width="26" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -595,8 +606,11 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="12" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>

--- a/jeaf-generator/src/main/resources/Breaking_Change_Report_Template.xlsx
+++ b/jeaf-generator/src/main/resources/Breaking_Change_Report_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C823A2-D35B-9242-AF25-689A1C616038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21213A85-80EA-254D-BE5D-82FA035F7A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4640" yWindow="620" windowWidth="29960" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
     <t>Go Live  Date</t>
   </si>
   <si>
-    <t>End of Compatibility Phase</t>
+    <t>End of Compatibility Period</t>
   </si>
 </sst>
 </file>
@@ -249,7 +249,7 @@
     <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live  Date" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{BA3D9D58-4D63-3545-A4C7-20399432C0A1}" name="End of Compatibility Phase" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{BA3D9D58-4D63-3545-A4C7-20399432C0A1}" name="End of Compatibility Period" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -581,7 +581,7 @@
     <col min="4" max="4" width="60.33203125" style="9" customWidth="1"/>
     <col min="5" max="5" width="31.5" style="10" customWidth="1"/>
     <col min="6" max="7" width="31.5" style="11" customWidth="1"/>
-    <col min="8" max="8" width="26" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.1640625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">

--- a/jeaf-generator/src/main/resources/Breaking_Change_Report_Template.xlsx
+++ b/jeaf-generator/src/main/resources/Breaking_Change_Report_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A25722-840F-934A-ACD6-3B8034AE6408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21213A85-80EA-254D-BE5D-82FA035F7A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4640" yWindow="620" windowWidth="29960" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Package</t>
   </si>
@@ -59,7 +59,10 @@
     <t>Active with</t>
   </si>
   <si>
-    <t>Activation Date</t>
+    <t>Go Live  Date</t>
+  </si>
+  <si>
+    <t>End of Compatibility Period</t>
   </si>
 </sst>
 </file>
@@ -128,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -142,32 +145,38 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -178,12 +187,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -210,11 +213,17 @@
       </border>
     </dxf>
     <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color theme="4"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -230,16 +239,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:G1048576" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4" headerRowBorderDxfId="10" tableBorderDxfId="9">
-  <autoFilter ref="A1:G1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Activation Date" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:H1048576" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
+  <autoFilter ref="A1:H1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live  Date" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{BA3D9D58-4D63-3545-A4C7-20399432C0A1}" name="End of Compatibility Period" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -562,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1136C3-A1B3-DD42-A00A-DCFCD8D149EA}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.5" style="9" customWidth="1"/>
@@ -571,9 +581,10 @@
     <col min="4" max="4" width="60.33203125" style="9" customWidth="1"/>
     <col min="5" max="5" width="31.5" style="10" customWidth="1"/>
     <col min="6" max="7" width="31.5" style="11" customWidth="1"/>
+    <col min="8" max="8" width="26.1640625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -595,8 +606,11 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="12" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
